--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486810_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486810_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>2.8629</v>
+        <v>3.791</v>
       </c>
       <c r="E2" t="n">
-        <v>3.3369</v>
+        <v>4.116</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.474</v>
+        <v>-0.325</v>
       </c>
       <c r="G2" t="n">
         <v>0.3498</v>
@@ -610,13 +610,13 @@
         <v>1.5446</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.2593</v>
+        <v>0.6688</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4966</v>
+        <v>0.2825</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2373</v>
+        <v>0.3863</v>
       </c>
       <c r="V2" t="n">
         <v>1.2277</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.1599</v>
+        <v>1.7516</v>
       </c>
       <c r="E3" t="n">
-        <v>2.8012</v>
+        <v>3.0702</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.6413</v>
+        <v>-1.3185</v>
       </c>
       <c r="G3" t="n">
         <v>-1.3718</v>
@@ -688,13 +688,13 @@
         <v>2.3169</v>
       </c>
       <c r="S3" t="n">
-        <v>0.4078</v>
+        <v>0.9996</v>
       </c>
       <c r="T3" t="n">
-        <v>0.3305</v>
+        <v>0.5995</v>
       </c>
       <c r="U3" t="n">
-        <v>0.07729999999999999</v>
+        <v>0.4001</v>
       </c>
       <c r="V3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>C. MURRAY</t>
+          <t>A. ANDRADE ROSSI</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0596</v>
+        <v>1.1433</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6652</v>
+        <v>3.0533</v>
       </c>
       <c r="F4" t="n">
-        <v>0.3943</v>
+        <v>-1.9101</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.7166</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.5659999999999999</v>
+        <v>-0.2204</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.1506</v>
+        <v>0.8952</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7399</v>
+        <v>4.0963</v>
       </c>
       <c r="K4" t="n">
-        <v>0.8144</v>
+        <v>1.5734</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0745</v>
+        <v>2.5229</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.4565</v>
+        <v>-3.4214</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.3804</v>
+        <v>-1.7937</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.0761</v>
+        <v>-1.6277</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.9654</v>
+        <v>0.5792</v>
       </c>
       <c r="Q4" t="n">
-        <v>-3.2823</v>
+        <v>-1.3515</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3169</v>
+        <v>1.9308</v>
       </c>
       <c r="S4" t="n">
-        <v>3.1277</v>
+        <v>1.1168</v>
       </c>
       <c r="T4" t="n">
-        <v>1.737</v>
+        <v>0.965</v>
       </c>
       <c r="U4" t="n">
-        <v>1.3907</v>
+        <v>0.1518</v>
       </c>
       <c r="V4" t="n">
-        <v>0.6138</v>
+        <v>-1.2277</v>
       </c>
       <c r="W4" t="n">
-        <v>1.4707</v>
+        <v>-0.6565</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.8568</v>
+        <v>-0.5712</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. VILLALBA BAULBYS</t>
+          <t>I. CONDES LOPEZ-CEPERO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9376</v>
+        <v>0.0125</v>
       </c>
       <c r="E5" t="n">
-        <v>3.0836</v>
+        <v>0.4021</v>
       </c>
       <c r="F5" t="n">
-        <v>-2.146</v>
+        <v>-0.3895</v>
       </c>
       <c r="G5" t="n">
-        <v>-4.9474</v>
+        <v>-0.7946</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.5655</v>
+        <v>-1.9656</v>
       </c>
       <c r="I5" t="n">
-        <v>-3.3819</v>
+        <v>1.171</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0468</v>
+        <v>0.0267</v>
       </c>
       <c r="K5" t="n">
-        <v>1.263</v>
+        <v>-1.2755</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.2162</v>
+        <v>1.3022</v>
       </c>
       <c r="M5" t="n">
-        <v>-4.9942</v>
+        <v>-0.8212</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.8285</v>
+        <v>-0.6901</v>
       </c>
       <c r="O5" t="n">
-        <v>-2.1657</v>
+        <v>-0.1311</v>
       </c>
       <c r="P5" t="n">
-        <v>0.5792</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.1585</v>
+        <v>-0.9654</v>
       </c>
       <c r="R5" t="n">
-        <v>1.7377</v>
+        <v>0.3862</v>
       </c>
       <c r="S5" t="n">
-        <v>3.4642</v>
+        <v>0.1587</v>
       </c>
       <c r="T5" t="n">
-        <v>2.0681</v>
+        <v>-0.1725</v>
       </c>
       <c r="U5" t="n">
-        <v>1.3962</v>
+        <v>0.3312</v>
       </c>
       <c r="V5" t="n">
-        <v>1.8415</v>
+        <v>1.2277</v>
       </c>
       <c r="W5" t="n">
-        <v>2.1271</v>
+        <v>1.5133</v>
       </c>
       <c r="X5" t="n">
         <v>-0.2856</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ANDRADE ROSSI</t>
+          <t>C. MURRAY</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8591</v>
+        <v>-0.3098</v>
       </c>
       <c r="E6" t="n">
-        <v>2.943</v>
+        <v>-0.3069</v>
       </c>
       <c r="F6" t="n">
-        <v>-2.0839</v>
+        <v>-0.003</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6749000000000001</v>
+        <v>-1.7166</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2204</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8952</v>
+        <v>-1.1506</v>
       </c>
       <c r="J6" t="n">
-        <v>4.0963</v>
+        <v>0.7399</v>
       </c>
       <c r="K6" t="n">
-        <v>1.5734</v>
+        <v>0.8144</v>
       </c>
       <c r="L6" t="n">
-        <v>2.5229</v>
+        <v>-0.0745</v>
       </c>
       <c r="M6" t="n">
-        <v>-3.4214</v>
+        <v>-2.4565</v>
       </c>
       <c r="N6" t="n">
-        <v>-1.7937</v>
+        <v>-1.3804</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.6277</v>
+        <v>-1.0761</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5792</v>
+        <v>-0.9654</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.3515</v>
+        <v>-3.2823</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9308</v>
+        <v>2.3169</v>
       </c>
       <c r="S6" t="n">
-        <v>0.8327</v>
+        <v>1.7583</v>
       </c>
       <c r="T6" t="n">
-        <v>0.8547</v>
+        <v>0.7649</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.022</v>
+        <v>0.9933999999999999</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.2277</v>
+        <v>0.6138</v>
       </c>
       <c r="W6" t="n">
-        <v>-0.6565</v>
+        <v>1.4707</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.5712</v>
+        <v>-0.8568</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>I. CONDES LOPEZ-CEPERO</t>
+          <t>M. TEVAR TEVAR</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.0412</v>
+        <v>-0.8964</v>
       </c>
       <c r="E7" t="n">
-        <v>0.2987</v>
+        <v>-0.6895</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.3399</v>
+        <v>-0.2069</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7946</v>
+        <v>-0.8964</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.9656</v>
+        <v>-0.2069</v>
       </c>
       <c r="I7" t="n">
-        <v>1.171</v>
+        <v>-0.6895</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0267</v>
+        <v>-0.6895</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.2755</v>
+        <v>0</v>
       </c>
       <c r="L7" t="n">
-        <v>1.3022</v>
+        <v>-0.6895</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8212</v>
+        <v>-0.2069</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.6901</v>
+        <v>-0.2069</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.1311</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.5792</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9654</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.3862</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>0.1049</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.2759</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3808</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>1.2277</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.5133</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.2856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. TEVAR TEVAR</t>
+          <t>M. VILLALBA BAULBYS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8964</v>
+        <v>-0.9959</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.6895</v>
+        <v>1.746</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2069</v>
+        <v>-2.742</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.8964</v>
+        <v>-4.9474</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.2069</v>
+        <v>-1.5655</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.6895</v>
+        <v>-3.3819</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.6895</v>
+        <v>0.0468</v>
       </c>
       <c r="K8" t="n">
-        <v>0</v>
+        <v>1.263</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.6895</v>
+        <v>-1.2162</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.2069</v>
+        <v>-4.9942</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2069</v>
+        <v>-2.8285</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>-2.1657</v>
       </c>
       <c r="P8" t="n">
-        <v>0</v>
+        <v>0.5792</v>
       </c>
       <c r="Q8" t="n">
-        <v>0</v>
+        <v>-1.1585</v>
       </c>
       <c r="R8" t="n">
-        <v>0</v>
+        <v>1.7377</v>
       </c>
       <c r="S8" t="n">
-        <v>0</v>
+        <v>1.5307</v>
       </c>
       <c r="T8" t="n">
-        <v>0</v>
+        <v>0.7305</v>
       </c>
       <c r="U8" t="n">
-        <v>0</v>
+        <v>0.8002</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>1.8415</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>2.1271</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.2856</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3465</v>
+        <v>-1.7505</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.2094</v>
+        <v>-1.4644</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1371</v>
+        <v>-0.2861</v>
       </c>
       <c r="G9" t="n">
         <v>-0.3462</v>
@@ -1156,13 +1156,13 @@
         <v>0.5792</v>
       </c>
       <c r="S9" t="n">
-        <v>0.7833</v>
+        <v>0.3793</v>
       </c>
       <c r="T9" t="n">
-        <v>0.1928</v>
+        <v>-0.0622</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5905</v>
+        <v>0.4415</v>
       </c>
       <c r="V9" t="n">
         <v>-2.1698</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.837</v>
+        <v>-2.5308</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.4792</v>
+        <v>-1.2724</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.3578</v>
+        <v>-1.2585</v>
       </c>
       <c r="G10" t="n">
         <v>-1.776</v>
@@ -1234,13 +1234,13 @@
         <v>0.7723</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.127</v>
+        <v>0.1792</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1932</v>
+        <v>0.0136</v>
       </c>
       <c r="U10" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.1655</v>
       </c>
       <c r="V10" t="n">
         <v>-1.5133</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-5.7625</v>
+        <v>-4.5323</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0603</v>
+        <v>-3.1777</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.7022</v>
+        <v>-1.3545</v>
       </c>
       <c r="G11" t="n">
         <v>-1.9035</v>
@@ -1312,13 +1312,13 @@
         <v>1.9308</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.789</v>
+        <v>0.4412</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.745</v>
+        <v>0.1375</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.044</v>
+        <v>0.3036</v>
       </c>
       <c r="V11" t="n">
         <v>0.9847</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-6.5087</v>
+        <v>-5.3682</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.6704</v>
+        <v>-3.6292</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.8383</v>
+        <v>-1.739</v>
       </c>
       <c r="G12" t="n">
         <v>-5.5462</v>
@@ -1390,13 +1390,13 @@
         <v>1.9308</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.3752</v>
+        <v>0.7653</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.7174</v>
+        <v>0.3238</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3421</v>
+        <v>0.4415</v>
       </c>
       <c r="V12" t="n">
         <v>0.5712</v>
@@ -1423,10 +1423,10 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-10.5132</v>
+        <v>-9.685499999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>1.019800000000001</v>
+        <v>1.847500000000001</v>
       </c>
       <c r="F13" t="n">
         <v>-11.5331</v>
@@ -1468,13 +1468,13 @@
         <v>15.4462</v>
       </c>
       <c r="S13" t="n">
-        <v>7.1701</v>
+        <v>7.9979</v>
       </c>
       <c r="T13" t="n">
-        <v>2.754999999999999</v>
+        <v>3.5826</v>
       </c>
       <c r="U13" t="n">
-        <v>4.415100000000002</v>
+        <v>4.415100000000001</v>
       </c>
       <c r="V13" t="n">
         <v>1.5558</v>
@@ -1483,7 +1483,7 @@
         <v>8.6662</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.1103</v>
+        <v>-7.110300000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>9.1341</v>
+        <v>8.8995</v>
       </c>
       <c r="E14" t="n">
         <v>7.1864</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9477</v>
+        <v>1.7131</v>
       </c>
       <c r="G14" t="n">
         <v>7.8179</v>
@@ -1546,13 +1546,13 @@
         <v>2.7031</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0274</v>
+        <v>-0.2619</v>
       </c>
       <c r="T14" t="n">
         <v>-0.7727000000000001</v>
       </c>
       <c r="U14" t="n">
-        <v>0.7453</v>
+        <v>0.5107</v>
       </c>
       <c r="V14" t="n">
         <v>0.5712</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.949</v>
+        <v>3.1862</v>
       </c>
       <c r="E15" t="n">
         <v>2.625</v>
       </c>
       <c r="F15" t="n">
-        <v>0.324</v>
+        <v>0.5612</v>
       </c>
       <c r="G15" t="n">
         <v>4.2305</v>
@@ -1624,13 +1624,13 @@
         <v>3.0892</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.9267</v>
+        <v>-0.6895</v>
       </c>
       <c r="T15" t="n">
         <v>-0.6071</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.3196</v>
+        <v>-0.0824</v>
       </c>
       <c r="V15" t="n">
         <v>-1.5133</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.8757</v>
+        <v>2.8012</v>
       </c>
       <c r="E16" t="n">
         <v>2.8055</v>
       </c>
       <c r="F16" t="n">
-        <v>0.0702</v>
+        <v>-0.0043</v>
       </c>
       <c r="G16" t="n">
         <v>0.7471</v>
@@ -1702,13 +1702,13 @@
         <v>2.3169</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.4081</v>
+        <v>-0.4825</v>
       </c>
       <c r="T16" t="n">
         <v>-0.6071</v>
       </c>
       <c r="U16" t="n">
-        <v>0.1991</v>
+        <v>0.1246</v>
       </c>
       <c r="V16" t="n">
         <v>1.1851</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.1174</v>
+        <v>2.3298</v>
       </c>
       <c r="E17" t="n">
         <v>1.898</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2194</v>
+        <v>0.4318</v>
       </c>
       <c r="G17" t="n">
         <v>1.8212</v>
@@ -1780,13 +1780,13 @@
         <v>1.9308</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.7776999999999999</v>
+        <v>-0.5653</v>
       </c>
       <c r="T17" t="n">
         <v>-0.3864</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3913</v>
+        <v>-0.1789</v>
       </c>
       <c r="V17" t="n">
         <v>-0.8568</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.4155</v>
+        <v>1.4541</v>
       </c>
       <c r="E18" t="n">
         <v>1.3654</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0501</v>
+        <v>0.0887</v>
       </c>
       <c r="G18" t="n">
         <v>3.4506</v>
@@ -1858,13 +1858,13 @@
         <v>1.3515</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.4245</v>
+        <v>-0.3859</v>
       </c>
       <c r="T18" t="n">
         <v>-0.3311</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.0934</v>
+        <v>-0.0548</v>
       </c>
       <c r="V18" t="n">
         <v>0.8995</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2779</v>
+        <v>-0.3772</v>
       </c>
       <c r="E20" t="n">
         <v>0.7298</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0076</v>
+        <v>-1.107</v>
       </c>
       <c r="G20" t="n">
         <v>1.1985</v>
@@ -2014,13 +2014,13 @@
         <v>0.7723</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8658</v>
+        <v>-0.9651999999999999</v>
       </c>
       <c r="T20" t="n">
         <v>-0.3863</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4796</v>
+        <v>-0.5789</v>
       </c>
       <c r="V20" t="n">
         <v>1.5133</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.6364</v>
+        <v>-0.5867</v>
       </c>
       <c r="E21" t="n">
         <v>-0.5382</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0982</v>
+        <v>-0.0486</v>
       </c>
       <c r="G21" t="n">
         <v>-0.9453</v>
@@ -2092,13 +2092,13 @@
         <v>0.9654</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6565</v>
+        <v>-0.6068</v>
       </c>
       <c r="T21" t="n">
         <v>-0.2759</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3806</v>
+        <v>-0.3309</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>J. LORENZO MEDINA</t>
+          <t>J. GARCIA CABRERA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.2879</v>
+        <v>-2.1388</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0283</v>
+        <v>-1.7521</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.2596</v>
+        <v>-0.3867</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.4629</v>
+        <v>-0.7599</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2346</v>
+        <v>-0.1246</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.2283</v>
+        <v>-0.6353</v>
       </c>
       <c r="J22" t="n">
-        <v>0.08210000000000001</v>
+        <v>-0.5659999999999999</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0414</v>
+        <v>0.0828</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0407</v>
+        <v>-0.6488</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.545</v>
+        <v>-0.1939</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2759</v>
+        <v>-0.2074</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.269</v>
+        <v>0.0135</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3862</v>
+        <v>-0.3862</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-0.9654</v>
       </c>
       <c r="R22" t="n">
-        <v>0.3862</v>
+        <v>0.5792</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3696</v>
+        <v>-0.9928</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.1104</v>
+        <v>-0.2207</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.2592</v>
+        <v>-0.7721</v>
       </c>
       <c r="V22" t="n">
-        <v>-1.8415</v>
+        <v>0</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-1.8415</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>J. GARCIA CABRERA</t>
+          <t>M. MOLINA HERRERA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-2.3375</v>
+        <v>-2.1724</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.7521</v>
+        <v>-2.7238</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5854</v>
+        <v>0.5514</v>
       </c>
       <c r="G23" t="n">
-        <v>-0.7599</v>
+        <v>1.2936</v>
       </c>
       <c r="H23" t="n">
-        <v>-0.1246</v>
+        <v>-1.2134</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.6353</v>
+        <v>2.507</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.5659999999999999</v>
+        <v>1.2055</v>
       </c>
       <c r="K23" t="n">
-        <v>0.0828</v>
+        <v>-0.178</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6488</v>
+        <v>1.3835</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1939</v>
+        <v>0.0881</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.2074</v>
+        <v>-1.0354</v>
       </c>
       <c r="O23" t="n">
-        <v>0.0135</v>
+        <v>1.1235</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.3862</v>
+        <v>-0.5792</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.9654</v>
+        <v>-2.8962</v>
       </c>
       <c r="R23" t="n">
-        <v>0.5792</v>
+        <v>2.3169</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.1915</v>
+        <v>-0.717</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2207</v>
+        <v>-0.6623</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.9707</v>
+        <v>-0.0547</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-2.1698</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>-0.3709</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-1.7989</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>M. MOLINA HERRERA</t>
+          <t>J. LORENZO MEDINA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-2.509</v>
+        <v>-2.263</v>
       </c>
       <c r="E24" t="n">
-        <v>-2.7238</v>
+        <v>-0.0283</v>
       </c>
       <c r="F24" t="n">
-        <v>0.2148</v>
+        <v>-2.2348</v>
       </c>
       <c r="G24" t="n">
-        <v>1.2936</v>
+        <v>-0.4629</v>
       </c>
       <c r="H24" t="n">
-        <v>-1.2134</v>
+        <v>-0.2346</v>
       </c>
       <c r="I24" t="n">
-        <v>2.507</v>
+        <v>-0.2283</v>
       </c>
       <c r="J24" t="n">
-        <v>1.2055</v>
+        <v>0.08210000000000001</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.178</v>
+        <v>0.0414</v>
       </c>
       <c r="L24" t="n">
-        <v>1.3835</v>
+        <v>0.0407</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0881</v>
+        <v>-0.545</v>
       </c>
       <c r="N24" t="n">
-        <v>-1.0354</v>
+        <v>-0.2759</v>
       </c>
       <c r="O24" t="n">
-        <v>1.1235</v>
+        <v>-0.269</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.5792</v>
+        <v>0.3862</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.8962</v>
+        <v>0</v>
       </c>
       <c r="R24" t="n">
-        <v>2.3169</v>
+        <v>0.3862</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.0536</v>
+        <v>-0.3448</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.6623</v>
+        <v>-0.1104</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.3913</v>
+        <v>-0.2344</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.1698</v>
+        <v>-1.8415</v>
       </c>
       <c r="W24" t="n">
-        <v>-0.3709</v>
+        <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.7989</v>
+        <v>-1.8415</v>
       </c>
     </row>
     <row r="25">
@@ -2359,19 +2359,19 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>10.5132</v>
+        <v>11.2029</v>
       </c>
       <c r="E25" t="n">
         <v>11.5332</v>
       </c>
       <c r="F25" t="n">
-        <v>-1.0199</v>
+        <v>-0.3304999999999993</v>
       </c>
       <c r="G25" t="n">
         <v>18.2739</v>
       </c>
       <c r="H25" t="n">
-        <v>6.552700000000001</v>
+        <v>6.552700000000002</v>
       </c>
       <c r="I25" t="n">
         <v>11.7212</v>
@@ -2395,7 +2395,7 @@
         <v>2.2715</v>
       </c>
       <c r="P25" t="n">
-        <v>0.9654000000000008</v>
+        <v>0.9654000000000007</v>
       </c>
       <c r="Q25" t="n">
         <v>-15.4464</v>
@@ -2404,13 +2404,13 @@
         <v>16.4115</v>
       </c>
       <c r="S25" t="n">
-        <v>-7.1703</v>
+        <v>-6.4806</v>
       </c>
       <c r="T25" t="n">
         <v>-4.4152</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.755</v>
+        <v>-2.0655</v>
       </c>
       <c r="V25" t="n">
         <v>-1.5558</v>
